--- a/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_MAR_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MAR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA976513-6EBC-47A5-936F-1D87A70A0347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{930C5AEC-256D-465B-8A89-28FC8C9921E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -663,13 +663,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S01aH02,S04aH04,S04aH05,S01aH04,S01aH03,S04aH02,S03aH04,S03aH03,S02aH03,S03aH05,S02aH04,S02aH05,S04aH03,S03aH02,S01aH05</t>
+    <t>S03aH04,S04aH02,S04aH05,S02aH04,S02aH05,S01aH04,S04aH03,S02aH02,S01aH03,S03aH02,S03aH05,S01aH05,S03aH03,S02aH03,S01aH02,S04aH04</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S03aH06,S01aH01,S04aH01,S04aH06,S02aH06,S02aH01,S01aH06</t>
+    <t>S02aH06,S02aH01,S03aH01,S01aH06,S01aH01,S04aH01,S04aH06,S03aH06</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH01,S03aH06,S01aH01,S04aH01,S04aH06,S02aH06,S02aH01,S01aH06</v>
+        <v>S02aH06,S02aH01,S03aH01,S01aH06,S01aH01,S04aH01,S04aH06,S03aH06</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH02,S01aH02,S04aH04,S04aH05,S01aH04,S01aH03,S04aH02,S03aH04,S03aH03,S02aH03,S03aH05,S02aH04,S02aH05,S04aH03,S03aH02,S01aH05</v>
+        <v>S03aH04,S04aH02,S04aH05,S02aH04,S02aH05,S01aH04,S04aH03,S02aH02,S01aH03,S03aH02,S03aH05,S01aH05,S03aH03,S02aH03,S01aH02,S04aH04</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1392,7 +1392,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B05E5ED1-8A8F-4940-AA4A-88DC2E18F687}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A10A92B-FC29-46AE-8A30-BAE559AB0967}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1498,7 +1498,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3EA0BE-1CF5-4B86-BC46-D23378D6B3E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE78B85-2376-4DA0-A6C7-ADFF78BDFBA1}">
   <dimension ref="B9:O586"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19128,7 +19128,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6A49A4-4F68-4EEC-B16E-75877F542863}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94DF858A-77F5-4308-BEA5-D6BCF890C0C5}">
   <dimension ref="B9:DH67"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29470,7 +29470,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0425E64E-2C98-473C-97A1-7D3299BC6355}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF5430A-90C1-4CDE-8CA4-73DAA1F27168}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29836,7 +29836,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC67B4CE-D3E9-4986-9E2B-489234124DFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31074034-FA8D-478E-A7D5-2F998729CE39}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30391,7 +30391,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99448958-6957-4416-89CC-8876ACFA3400}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83D81BC-2BA5-41C7-A912-EEA11346D7F6}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30682,7 +30682,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7381AC95-D132-4595-BEDE-1E147CFBA674}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6558BC3F-BFBD-4EFB-AC54-CBF82DD4C003}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31148,7 +31148,7 @@
         <v>45</v>
       </c>
       <c r="D42">
-        <v>0.11346666666666667</v>
+        <v>0.11346666666666666</v>
       </c>
       <c r="E42" t="s">
         <v>215</v>
@@ -31204,7 +31204,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>9.3833333333333338E-2</v>
+        <v>9.3833333333333324E-2</v>
       </c>
       <c r="E46" t="s">
         <v>215</v>
@@ -31372,7 +31372,7 @@
         <v>45</v>
       </c>
       <c r="D58">
-        <v>0.14709999999999998</v>
+        <v>0.14710000000000001</v>
       </c>
       <c r="E58" t="s">
         <v>215</v>
@@ -31652,7 +31652,7 @@
         <v>45</v>
       </c>
       <c r="D78">
-        <v>0.17656666666666668</v>
+        <v>0.17656666666666665</v>
       </c>
       <c r="E78" t="s">
         <v>215</v>
@@ -31932,7 +31932,7 @@
         <v>45</v>
       </c>
       <c r="D98">
-        <v>0.13753333333333331</v>
+        <v>0.13753333333333334</v>
       </c>
       <c r="E98" t="s">
         <v>215</v>
@@ -32268,7 +32268,7 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>0.18910000000000002</v>
+        <v>0.18909999999999996</v>
       </c>
       <c r="E122" t="s">
         <v>215</v>
